--- a/docs/downloads/04/tbl_cm_act_alaotra_feramanga_atsimo.xlsx
+++ b/docs/downloads/04/tbl_cm_act_alaotra_feramanga_atsimo.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,14 +384,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D2">
-        <v>15.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="3">
@@ -402,14 +402,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>4.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4">
@@ -420,7 +420,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C4">
@@ -438,14 +438,8 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>10</v>
-      </c>
-      <c r="D5">
-        <v>11.2</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -456,32 +450,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>1.1</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>113</v>
-      </c>
-      <c r="D7">
-        <v>22.3</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -492,14 +480,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="C8">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="D8">
-        <v>4.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="9">
@@ -510,14 +498,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C9">
-        <v>305</v>
+        <v>28</v>
       </c>
       <c r="D9">
-        <v>60.2</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
@@ -528,14 +516,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C10">
-        <v>63</v>
+        <v>305</v>
       </c>
       <c r="D10">
-        <v>12.4</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="11">
@@ -546,14 +534,50 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>63</v>
+      </c>
+      <c r="D12">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>33</v>
+      </c>
+      <c r="D13">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
